--- a/backend/src/main/resources/templates/PLANTILLA_PLANILLA_PROCESO_CTN.xlsx
+++ b/backend/src/main/resources/templates/PLANTILLA_PLANILLA_PROCESO_CTN.xlsx
@@ -617,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -693,6 +693,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1403,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BQ15"/>
+  <dimension ref="A1:BQ16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
@@ -2338,8 +2341,19 @@
       <c r="BO15" s="10"/>
       <c r="BP15" s="10"/>
     </row>
+    <row r="16" spans="60:68" x14ac:dyDescent="0.25">
+      <c r="BH16" s="26"/>
+      <c r="BI16" s="26"/>
+      <c r="BJ16" s="26"/>
+      <c r="BK16" s="26"/>
+      <c r="BL16" s="26"/>
+      <c r="BM16" s="26"/>
+      <c r="BN16" s="26"/>
+      <c r="BO16" s="26"/>
+      <c r="BP16" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="A1:AZ1"/>
     <mergeCell ref="A2:AZ2"/>
     <mergeCell ref="A3:AZ3"/>
@@ -2363,6 +2377,7 @@
     <mergeCell ref="BP6:BP7"/>
     <mergeCell ref="BQ6:BQ7"/>
     <mergeCell ref="BH15:BP15"/>
+    <mergeCell ref="BH16:BP16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/backend/src/main/resources/templates/PLANTILLA_PLANILLA_PROCESO_CTN.xlsx
+++ b/backend/src/main/resources/templates/PLANTILLA_PLANILLA_PROCESO_CTN.xlsx
@@ -1,547 +1,596 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="5"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="LEYENDA_PARA_DESARROLLO" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="PLANTILLA_ETAPA_1" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="PLANTILLA_ETAPA_2" state="visible" r:id="rId6"/>
+    <sheet name="LEYENDA_PARA_DESARROLLO" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="PLANTILLA_ETAPA_1" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="PLANTILLA_ETAPA_2" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="155">
   <si>
-    <t>PLANTILLA — PLANILLA DE PROCESO (CTN)</t>
-  </si>
-  <si>
-    <t>Esta hoja es solo documentación. No se exporta.</t>
-  </si>
-  <si>
-    <t>Hojas de datos:</t>
-  </si>
-  <si>
-    <t>PLANTILLA_ETAPA_1 y PLANTILLA_ETAPA_2 (una por etapa).</t>
-  </si>
-  <si>
-    <t>— ESTRUCTURA COMÚN —</t>
-  </si>
-  <si>
-    <t>Fila de encabezado de mes</t>
-  </si>
-  <si>
-    <t>Fila 6</t>
-  </si>
-  <si>
-    <t>Fila de título de instrumento (tarea)</t>
-  </si>
-  <si>
-    <t>Fila 7</t>
-  </si>
-  <si>
-    <t>Fila TP (puntaje máximo por instrumento)</t>
-  </si>
-  <si>
-    <t>Fila 8</t>
-  </si>
-  <si>
-    <t>Primera fila de alumno</t>
-  </si>
-  <si>
-    <t>Fila 9 (agregar/quitar filas debajo)</t>
-  </si>
-  <si>
-    <t>Columnas por bloque de mes</t>
-  </si>
-  <si>
-    <t>12 columnas de instrumento + 1 de Subtotal = 13 columnas</t>
-  </si>
-  <si>
-    <t>Cantidad de bloques de mes por etapa</t>
-  </si>
-  <si>
-    <t>5 (ajustar según los meses reales con tareas)</t>
-  </si>
-  <si>
-    <t>— ETAPA 1 (hoja PLANTILLA_ETAPA_1) —</t>
-  </si>
-  <si>
-    <t>Columna N°</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Columna Apellidos y Nombres</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Primer bloque de mes (Marzo)</t>
-  </si>
-  <si>
-    <t>Columna C</t>
-  </si>
-  <si>
-    <t>Columna Total General</t>
-  </si>
-  <si>
-    <t>Columna BP</t>
-  </si>
-  <si>
-    <t>Columna Calificación Final 1ª Etapa</t>
-  </si>
-  <si>
-    <t>Columna BQ</t>
-  </si>
-  <si>
-    <t>— ETAPA 2 (hoja PLANTILLA_ETAPA_2) —</t>
-  </si>
-  <si>
-    <t>Columna Calificación Final 1ª Etapa (heredada)</t>
-  </si>
-  <si>
-    <t>Primer bloque de mes (Julio)</t>
-  </si>
-  <si>
-    <t>Columna D</t>
-  </si>
-  <si>
-    <t>Columna Calificación Final 2ª Etapa</t>
-  </si>
-  <si>
-    <t>Columna BR</t>
-  </si>
-  <si>
-    <t>Columna Sumatoria 1° y 2° Etapa</t>
-  </si>
-  <si>
-    <t>Columna BS</t>
-  </si>
-  <si>
-    <t>Columna Calificación Final (promedio)</t>
-  </si>
-  <si>
-    <t>Columna BT</t>
-  </si>
-  <si>
-    <t>Columna Período Complementario</t>
-  </si>
-  <si>
-    <t>Columna BU (sin dato de origen aún — opcional)</t>
-  </si>
-  <si>
-    <t>Columna Período Regularización</t>
-  </si>
-  <si>
-    <t>Columna BV (sin dato de origen aún — opcional)</t>
-  </si>
-  <si>
-    <t>— MARCADORES {{...}} A REEMPLAZAR POR EL PROGRAMA —</t>
-  </si>
-  <si>
-    <t>{{DISCIPLINA}}</t>
-  </si>
-  <si>
-    <t>materia.getNombre() (o el nombre de la disciplina)</t>
-  </si>
-  <si>
-    <t>{{ESPECIALIDAD}}</t>
-  </si>
-  <si>
-    <t>curso.getEspecialidad()</t>
-  </si>
-  <si>
-    <t>{{PROFESOR}}</t>
-  </si>
-  <si>
-    <t>user.getFullName()</t>
-  </si>
-  <si>
-    <t>{{CURSO}} / {{TURNO}} / {{SECCION}}</t>
-  </si>
-  <si>
-    <t>curso.getCursoOrdinal() / turno / curso.getSeccion()</t>
-  </si>
-  <si>
-    <t>{{ANIO}}</t>
-  </si>
-  <si>
-    <t>AcademicPeriod.current() o el año de la planilla</t>
-  </si>
-  <si>
-    <t>{{MES_n_NOMBRE}}</t>
-  </si>
-  <si>
-    <t>Nombre del mes, agrupando las Tarea por Tarea.getFecha().getMonth()</t>
-  </si>
-  <si>
-    <t>{{MES_n_INSTR_j}}</t>
-  </si>
-  <si>
-    <t>Tarea.getTitulo() de la j-ésima tarea de ese mes</t>
-  </si>
-  <si>
-    <t>{{ALUMNO_NOMBRE}}</t>
-  </si>
-  <si>
-    <t>StudentRow.getAlumnoNombre()</t>
-  </si>
-  <si>
-    <t>— REGLAS DE FORMULA / CÁLCULO —</t>
-  </si>
-  <si>
-    <t>Subtotal de mes</t>
-  </si>
-  <si>
-    <t>SUMA de las columnas de instrumento de ese mes (ya en la plantilla)</t>
-  </si>
-  <si>
-    <t>Total General</t>
-  </si>
-  <si>
-    <t>SUMA de todos los Subtotales de mes (ya en la plantilla)</t>
-  </si>
-  <si>
-    <t>Calificación Final</t>
-  </si>
-  <si>
-    <t>NO se replica la fórmula de Excel: el valor final se escribe como número literal desde Java usando Planilla.getNotaForSum(), que ya implementa la misma lógica de umbrales que usa la planilla oficial en papel. Evita duplicar la regla en dos lugares.</t>
-  </si>
-  <si>
-    <t>Fila TP</t>
-  </si>
-  <si>
-    <t>Puntaje máximo de cada instrumento = Tarea.getTotal(); no es una fila de alumno.</t>
-  </si>
-  <si>
-    <t>— LÍMITE DE INSTRUMENTOS POR MES —</t>
-  </si>
-  <si>
-    <t>La plantilla reserva 12 columnas por mes (el máximo observado en los datos reales fue 5). Si una materia tiene más de 12 tareas en un mismo mes, hay que decidir: (a) fusionar/resumir tareas, (b) insertar columnas adicionales copiando el estilo de una columna vecina, o (c) aumentar INSTR_POR_MES en build_template.py y regenerar la plantilla.</t>
-  </si>
-  <si>
-    <t>COLEGIO TÉCNICO NACIONAL DE ASUNCIÓN</t>
-  </si>
-  <si>
-    <t>Servicio de Evaluación</t>
-  </si>
-  <si>
-    <t>PLANILLA DE PROCESO - 1º ETAPA</t>
-  </si>
-  <si>
-    <t>Disciplina: {{DISCIPLINA}}</t>
-  </si>
-  <si>
-    <t>Especialidad: {{ESPECIALIDAD}}</t>
-  </si>
-  <si>
-    <t>Profesor/a: {{PROFESOR}}</t>
-  </si>
-  <si>
-    <t>Curso: {{CURSO}}°   Turno: {{TURNO}}   Sección: "{{SECCION}}"</t>
-  </si>
-  <si>
-    <t>Año: {{ANIO}}</t>
-  </si>
-  <si>
-    <t>N°</t>
-  </si>
-  <si>
-    <t>Apellidos y Nombres</t>
-  </si>
-  <si>
-    <t>{{MES_1_NOMBRE}}</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>{{MES_2_NOMBRE}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_NOMBRE}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_NOMBRE}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_NOMBRE}}</t>
-  </si>
-  <si>
-    <t>Calificación Final 1º Etapa</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_1}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_2}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_3}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_4}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_5}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_6}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_7}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_8}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_9}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_10}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_11}}</t>
-  </si>
-  <si>
-    <t>{{MES_1_INSTR_12}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_1}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_2}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_3}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_4}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_5}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_6}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_7}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_8}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_9}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_10}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_11}}</t>
-  </si>
-  <si>
-    <t>{{MES_2_INSTR_12}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_1}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_2}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_3}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_4}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_5}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_6}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_7}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_8}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_9}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_10}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_11}}</t>
-  </si>
-  <si>
-    <t>{{MES_3_INSTR_12}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_1}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_2}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_3}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_4}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_5}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_6}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_7}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_8}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_9}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_10}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_11}}</t>
-  </si>
-  <si>
-    <t>{{MES_4_INSTR_12}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_1}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_2}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_3}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_4}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_5}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_6}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_7}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_8}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_9}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_10}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_11}}</t>
-  </si>
-  <si>
-    <t>{{MES_5_INSTR_12}}</t>
-  </si>
-  <si>
-    <t>TP</t>
-  </si>
-  <si>
-    <t>(puntaje máximo)</t>
-  </si>
-  <si>
-    <t>Firma del Docente</t>
-  </si>
-  <si>
-    <t>PLANILLA DE PROCESO - 2º ETAPA</t>
-  </si>
-  <si>
-    <t>Calificación Final 2º Etapa</t>
-  </si>
-  <si>
-    <t>Sumatoria 1° y 2° Etapa</t>
-  </si>
-  <si>
-    <t>Período Complementario</t>
-  </si>
-  <si>
-    <t>Período Regularización</t>
+    <t xml:space="preserve">PLANTILLA — PLANILLA DE PROCESO (CTN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esta hoja es solo documentación. No se exporta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hojas de datos:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANTILLA_ETAPA_1 y PLANTILLA_ETAPA_2 (una por etapa).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— ESTRUCTURA COMÚN —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila de encabezado de mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila de título de instrumento (tarea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila TP (puntaje máximo por instrumento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primera fila de alumno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila 9 (agregar/quitar filas debajo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columnas por bloque de mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 columnas de instrumento + 1 de Subtotal = 13 columnas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad de bloques de mes por etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (ajustar según los meses reales con tareas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— ETAPA 1 (hoja PLANTILLA_ETAPA_1) —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna N°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Apellidos y Nombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primer bloque de mes (Marzo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Total General</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna BP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Calificación Final 1ª Etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna BQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— ETAPA 2 (hoja PLANTILLA_ETAPA_2) —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Calificación Final 1ª Etapa (heredada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primer bloque de mes (Julio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Calificación Final 2ª Etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Sumatoria 1° y 2° Etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna BS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Calificación Final (promedio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna BT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Período Complementario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna BU (sin dato de origen aún — opcional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna Período Regularización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columna BV (sin dato de origen aún — opcional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— MARCADORES {{...}} A REEMPLAZAR POR EL PROGRAMA —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{DISCIPLINA}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">materia.getNombre() (o el nombre de la disciplina)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{ESPECIALIDAD}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curso.getEspecialidad()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{PROFESOR}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user.getFullName()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{CURSO}} / {{TURNO}} / {{SECCION}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curso.getCursoOrdinal() / turno / curso.getSeccion()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{ANIO}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AcademicPeriod.current() o el año de la planilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_n_NOMBRE}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre del mes, agrupando las Tarea por Tarea.getFecha().getMonth()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_n_INSTR_j}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarea.getTitulo() de la j-ésima tarea de ese mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{ALUMNO_NOMBRE}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StudentRow.getAlumnoNombre()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— REGLAS DE FORMULA / CÁLCULO —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal de mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMA de las columnas de instrumento de ese mes (ya en la plantilla)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total General</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMA de todos los Subtotales de mes (ya en la plantilla)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calificación Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO se replica la fórmula de Excel: el valor final se escribe como número literal desde Java usando Planilla.getNotaForSum(), que ya implementa la misma lógica de umbrales que usa la planilla oficial en papel. Evita duplicar la regla en dos lugares.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila TP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puntaje máximo de cada instrumento = Tarea.getTotal(); no es una fila de alumno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— LÍMITE DE INSTRUMENTOS POR MES —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La plantilla reserva 12 columnas por mes (el máximo observado en los datos reales fue 5). Si una materia tiene más de 12 tareas en un mismo mes, hay que decidir: (a) fusionar/resumir tareas, (b) insertar columnas adicionales copiando el estilo de una columna vecina, o (c) aumentar INSTR_POR_MES en build_template.py y regenerar la plantilla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLEGIO TÉCNICO NACIONAL DE ASUNCIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servicio de Evaluación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANILLA DE PROCESO - 1º ETAPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disciplina: {{DISCIPLINA}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especialidad: {{ESPECIALIDAD}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profesor/a: {{PROFESOR}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curso: {{CURSO}}°   Turno: {{TURNO}}   Sección: "{{SECCION}}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año: {{ANIO}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apellidos y Nombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_NOMBRE}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_NOMBRE}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_NOMBRE}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_NOMBRE}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_NOMBRE}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calificación Final 1º Etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_1}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_2}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_3}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_4}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_5}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_6}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_7}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_8}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_9}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_10}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_11}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_1_INSTR_12}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_1}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_2}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_3}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_4}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_5}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_6}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_7}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_8}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_9}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_10}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_11}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_2_INSTR_12}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_1}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_2}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_3}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_4}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_5}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_6}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_7}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_8}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_9}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_10}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_11}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_3_INSTR_12}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_1}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_2}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_3}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_4}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_5}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_6}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_7}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_8}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_9}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_10}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_11}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_4_INSTR_12}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_1}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_2}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_3}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_4}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_5}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_6}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_7}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_8}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_9}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_10}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_11}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{MES_5_INSTR_12}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(puntaje máximo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firma del Docente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANILLA DE PROCESO - 2º ETAPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calificación Final 2º Etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumatoria 1° y 2° Etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Período Complementario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Período Regularización</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="15">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
+      <sz val="16"/>
       <color rgb="FF2E5395"/>
-      <sz val="16"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -554,23 +603,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE4DFEC"/>
+        <bgColor rgb="FFD8E4BC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD8E4BC"/>
+        <bgColor rgb="FFE4DFEC"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
         <color rgb="FF808080"/>
       </left>
@@ -585,7 +636,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
         <color rgb="FF808080"/>
       </left>
@@ -598,7 +649,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -614,115 +665,274 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+  <cellXfs count="30">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE4DFEC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF2E5395"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8E4BC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFE4DFEC"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD8E4BC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF2E5395"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -757,314 +967,169 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="42.142857142857146" customWidth="1"/>
-    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="3" style="0" width="13.57"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1072,17 +1137,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -1090,7 +1155,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1098,7 +1163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -1106,7 +1171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -1114,7 +1179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -1122,7 +1187,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -1130,17 +1195,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -1148,7 +1213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
@@ -1156,7 +1221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
@@ -1164,7 +1229,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>24</v>
       </c>
@@ -1172,7 +1237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>26</v>
       </c>
@@ -1180,17 +1245,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
@@ -1198,7 +1263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>20</v>
       </c>
@@ -1206,7 +1271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
@@ -1214,7 +1279,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
@@ -1222,7 +1287,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>24</v>
       </c>
@@ -1230,7 +1295,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>32</v>
       </c>
@@ -1238,7 +1303,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>34</v>
       </c>
@@ -1246,7 +1311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>36</v>
       </c>
@@ -1254,7 +1319,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
@@ -1262,7 +1327,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -1270,17 +1335,17 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
     </row>
-    <row r="34" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="2"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>43</v>
       </c>
@@ -1288,7 +1353,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>45</v>
       </c>
@@ -1296,7 +1361,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>47</v>
       </c>
@@ -1304,7 +1369,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>49</v>
       </c>
@@ -1312,7 +1377,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>51</v>
       </c>
@@ -1320,7 +1385,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>53</v>
       </c>
@@ -1328,7 +1393,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>55</v>
       </c>
@@ -1336,7 +1401,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>57</v>
       </c>
@@ -1344,17 +1409,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>60</v>
       </c>
@@ -1362,7 +1427,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>62</v>
       </c>
@@ -1370,7 +1435,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" ht="55.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>64</v>
       </c>
@@ -1378,7 +1443,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="48" ht="28.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
@@ -1386,11 +1451,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
     </row>
-    <row r="50" ht="69" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>68</v>
       </c>
@@ -1399,22 +1464,39 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:BQ16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="69" width="9.285714285714286" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="16" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="29" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="42" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="55" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="67" style="0" width="9.29"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>70</v>
       </c>
@@ -1470,7 +1552,7 @@
       <c r="AY1" s="4"/>
       <c r="AZ1" s="4"/>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>71</v>
       </c>
@@ -1526,7 +1608,7 @@
       <c r="AY2" s="5"/>
       <c r="AZ2" s="5"/>
     </row>
-    <row r="3" ht="21" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>72</v>
       </c>
@@ -1582,7 +1664,7 @@
       <c r="AY3" s="6"/>
       <c r="AZ3" s="6"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>73</v>
       </c>
@@ -1602,7 +1684,7 @@
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>75</v>
       </c>
@@ -1632,7 +1714,7 @@
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>78</v>
       </c>
@@ -1731,7 +1813,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" ht="129.75" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="92.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="17" t="s">
@@ -1922,7 +2004,7 @@
       <c r="BP7" s="15"/>
       <c r="BQ7" s="16"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
         <v>147</v>
       </c>
@@ -1941,8 +2023,9 @@
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
-      <c r="O8" s="20">
-        <f>SUM(C8:N8)</f>
+      <c r="O8" s="20" t="n">
+        <f aca="false">SUM(C8:N8)</f>
+        <v>0</v>
       </c>
       <c r="P8" s="19"/>
       <c r="Q8" s="19"/>
@@ -1956,8 +2039,9 @@
       <c r="Y8" s="19"/>
       <c r="Z8" s="19"/>
       <c r="AA8" s="19"/>
-      <c r="AB8" s="20">
-        <f>SUM(P8:AA8)</f>
+      <c r="AB8" s="20" t="n">
+        <f aca="false">SUM(P8:AA8)</f>
+        <v>0</v>
       </c>
       <c r="AC8" s="19"/>
       <c r="AD8" s="19"/>
@@ -1971,8 +2055,9 @@
       <c r="AL8" s="19"/>
       <c r="AM8" s="19"/>
       <c r="AN8" s="19"/>
-      <c r="AO8" s="20">
-        <f>SUM(AC8:AN8)</f>
+      <c r="AO8" s="20" t="n">
+        <f aca="false">SUM(AC8:AN8)</f>
+        <v>0</v>
       </c>
       <c r="AP8" s="19"/>
       <c r="AQ8" s="19"/>
@@ -1986,8 +2071,9 @@
       <c r="AY8" s="19"/>
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
-      <c r="BB8" s="20">
-        <f>SUM(AP8:BA8)</f>
+      <c r="BB8" s="20" t="n">
+        <f aca="false">SUM(AP8:BA8)</f>
+        <v>0</v>
       </c>
       <c r="BC8" s="19"/>
       <c r="BD8" s="19"/>
@@ -2001,15 +2087,17 @@
       <c r="BL8" s="19"/>
       <c r="BM8" s="19"/>
       <c r="BN8" s="19"/>
-      <c r="BO8" s="20">
-        <f>SUM(BC8:BN8)</f>
-      </c>
-      <c r="BP8" s="21">
-        <f>SUM(O8+AB8+AO8+BB8+BO8)</f>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="BO8" s="20" t="n">
+        <f aca="false">SUM(BC8:BN8)</f>
+        <v>0</v>
+      </c>
+      <c r="BP8" s="21" t="n">
+        <f aca="false">SUM(O8+AB8+AO8+BB8+BO8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="23" t="s">
@@ -2027,8 +2115,9 @@
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
-      <c r="O9" s="24">
-        <f>SUM(C9:N9)</f>
+      <c r="O9" s="24" t="n">
+        <f aca="false">SUM(C9:N9)</f>
+        <v>0</v>
       </c>
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
@@ -2042,8 +2131,9 @@
       <c r="Y9" s="19"/>
       <c r="Z9" s="19"/>
       <c r="AA9" s="19"/>
-      <c r="AB9" s="24">
-        <f>SUM(P9:AA9)</f>
+      <c r="AB9" s="24" t="n">
+        <f aca="false">SUM(P9:AA9)</f>
+        <v>0</v>
       </c>
       <c r="AC9" s="19"/>
       <c r="AD9" s="19"/>
@@ -2057,8 +2147,9 @@
       <c r="AL9" s="19"/>
       <c r="AM9" s="19"/>
       <c r="AN9" s="19"/>
-      <c r="AO9" s="24">
-        <f>SUM(AC9:AN9)</f>
+      <c r="AO9" s="24" t="n">
+        <f aca="false">SUM(AC9:AN9)</f>
+        <v>0</v>
       </c>
       <c r="AP9" s="19"/>
       <c r="AQ9" s="19"/>
@@ -2072,8 +2163,9 @@
       <c r="AY9" s="19"/>
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
-      <c r="BB9" s="24">
-        <f>SUM(AP9:BA9)</f>
+      <c r="BB9" s="24" t="n">
+        <f aca="false">SUM(AP9:BA9)</f>
+        <v>0</v>
       </c>
       <c r="BC9" s="19"/>
       <c r="BD9" s="19"/>
@@ -2087,16 +2179,18 @@
       <c r="BL9" s="19"/>
       <c r="BM9" s="19"/>
       <c r="BN9" s="19"/>
-      <c r="BO9" s="24">
-        <f>SUM(BC9:BN9)</f>
-      </c>
-      <c r="BP9" s="21">
-        <f>SUM(O9+AB9+AO9+BB9+BO9)</f>
+      <c r="BO9" s="24" t="n">
+        <f aca="false">SUM(BC9:BN9)</f>
+        <v>0</v>
+      </c>
+      <c r="BP9" s="21" t="n">
+        <f aca="false">SUM(O9+AB9+AO9+BB9+BO9)</f>
+        <v>0</v>
       </c>
       <c r="BQ9" s="25"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="n">
         <v>2</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2114,8 +2208,9 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
-      <c r="O10" s="24">
-        <f>SUM(C10:N10)</f>
+      <c r="O10" s="24" t="n">
+        <f aca="false">SUM(C10:N10)</f>
+        <v>0</v>
       </c>
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
@@ -2129,8 +2224,9 @@
       <c r="Y10" s="19"/>
       <c r="Z10" s="19"/>
       <c r="AA10" s="19"/>
-      <c r="AB10" s="24">
-        <f>SUM(P10:AA10)</f>
+      <c r="AB10" s="24" t="n">
+        <f aca="false">SUM(P10:AA10)</f>
+        <v>0</v>
       </c>
       <c r="AC10" s="19"/>
       <c r="AD10" s="19"/>
@@ -2144,8 +2240,9 @@
       <c r="AL10" s="19"/>
       <c r="AM10" s="19"/>
       <c r="AN10" s="19"/>
-      <c r="AO10" s="24">
-        <f>SUM(AC10:AN10)</f>
+      <c r="AO10" s="24" t="n">
+        <f aca="false">SUM(AC10:AN10)</f>
+        <v>0</v>
       </c>
       <c r="AP10" s="19"/>
       <c r="AQ10" s="19"/>
@@ -2159,8 +2256,9 @@
       <c r="AY10" s="19"/>
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
-      <c r="BB10" s="24">
-        <f>SUM(AP10:BA10)</f>
+      <c r="BB10" s="24" t="n">
+        <f aca="false">SUM(AP10:BA10)</f>
+        <v>0</v>
       </c>
       <c r="BC10" s="19"/>
       <c r="BD10" s="19"/>
@@ -2174,16 +2272,18 @@
       <c r="BL10" s="19"/>
       <c r="BM10" s="19"/>
       <c r="BN10" s="19"/>
-      <c r="BO10" s="24">
-        <f>SUM(BC10:BN10)</f>
-      </c>
-      <c r="BP10" s="21">
-        <f>SUM(O10+AB10+AO10+BB10+BO10)</f>
+      <c r="BO10" s="24" t="n">
+        <f aca="false">SUM(BC10:BN10)</f>
+        <v>0</v>
+      </c>
+      <c r="BP10" s="21" t="n">
+        <f aca="false">SUM(O10+AB10+AO10+BB10+BO10)</f>
+        <v>0</v>
       </c>
       <c r="BQ10" s="25"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="n">
         <v>3</v>
       </c>
       <c r="B11" s="23" t="s">
@@ -2201,8 +2301,9 @@
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
-      <c r="O11" s="24">
-        <f>SUM(C11:N11)</f>
+      <c r="O11" s="24" t="n">
+        <f aca="false">SUM(C11:N11)</f>
+        <v>0</v>
       </c>
       <c r="P11" s="19"/>
       <c r="Q11" s="19"/>
@@ -2216,8 +2317,9 @@
       <c r="Y11" s="19"/>
       <c r="Z11" s="19"/>
       <c r="AA11" s="19"/>
-      <c r="AB11" s="24">
-        <f>SUM(P11:AA11)</f>
+      <c r="AB11" s="24" t="n">
+        <f aca="false">SUM(P11:AA11)</f>
+        <v>0</v>
       </c>
       <c r="AC11" s="19"/>
       <c r="AD11" s="19"/>
@@ -2231,8 +2333,9 @@
       <c r="AL11" s="19"/>
       <c r="AM11" s="19"/>
       <c r="AN11" s="19"/>
-      <c r="AO11" s="24">
-        <f>SUM(AC11:AN11)</f>
+      <c r="AO11" s="24" t="n">
+        <f aca="false">SUM(AC11:AN11)</f>
+        <v>0</v>
       </c>
       <c r="AP11" s="19"/>
       <c r="AQ11" s="19"/>
@@ -2246,8 +2349,9 @@
       <c r="AY11" s="19"/>
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
-      <c r="BB11" s="24">
-        <f>SUM(AP11:BA11)</f>
+      <c r="BB11" s="24" t="n">
+        <f aca="false">SUM(AP11:BA11)</f>
+        <v>0</v>
       </c>
       <c r="BC11" s="19"/>
       <c r="BD11" s="19"/>
@@ -2261,15 +2365,17 @@
       <c r="BL11" s="19"/>
       <c r="BM11" s="19"/>
       <c r="BN11" s="19"/>
-      <c r="BO11" s="24">
-        <f>SUM(BC11:BN11)</f>
-      </c>
-      <c r="BP11" s="21">
-        <f>SUM(O11+AB11+AO11+BB11+BO11)</f>
+      <c r="BO11" s="24" t="n">
+        <f aca="false">SUM(BC11:BN11)</f>
+        <v>0</v>
+      </c>
+      <c r="BP11" s="21" t="n">
+        <f aca="false">SUM(O11+AB11+AO11+BB11+BO11)</f>
+        <v>0</v>
       </c>
       <c r="BQ11" s="25"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2341,7 +2447,7 @@
       <c r="BO15" s="10"/>
       <c r="BP15" s="10"/>
     </row>
-    <row r="16" spans="60:68" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="BH16" s="26"/>
       <c r="BI16" s="26"/>
       <c r="BJ16" s="26"/>
@@ -2362,39 +2468,57 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:R5"/>
     <mergeCell ref="T5:V5"/>
-    <mergeCell ref="C6:N6"/>
-    <mergeCell ref="P6:AA6"/>
-    <mergeCell ref="AC6:AN6"/>
-    <mergeCell ref="AP6:BA6"/>
-    <mergeCell ref="BC6:BN6"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:N6"/>
     <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:AA6"/>
     <mergeCell ref="AB6:AB7"/>
+    <mergeCell ref="AC6:AN6"/>
     <mergeCell ref="AO6:AO7"/>
+    <mergeCell ref="AP6:BA6"/>
     <mergeCell ref="BB6:BB7"/>
+    <mergeCell ref="BC6:BN6"/>
     <mergeCell ref="BO6:BO7"/>
     <mergeCell ref="BP6:BP7"/>
     <mergeCell ref="BQ6:BQ7"/>
     <mergeCell ref="BH15:BP15"/>
     <mergeCell ref="BH16:BP16"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:BV15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="74" width="9.285714285714286" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="17" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="30" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="43" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="56" style="0" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="68" style="0" width="9.29"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>70</v>
       </c>
@@ -2450,7 +2574,7 @@
       <c r="AY1" s="4"/>
       <c r="AZ1" s="4"/>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>71</v>
       </c>
@@ -2506,7 +2630,7 @@
       <c r="AY2" s="5"/>
       <c r="AZ2" s="5"/>
     </row>
-    <row r="3" ht="21" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>150</v>
       </c>
@@ -2562,7 +2686,7 @@
       <c r="AY3" s="6"/>
       <c r="AZ3" s="6"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>73</v>
       </c>
@@ -2582,7 +2706,7 @@
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>75</v>
       </c>
@@ -2612,14 +2736,14 @@
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>78</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="27" t="s">
         <v>86</v>
       </c>
       <c r="D6" s="13" t="s">
@@ -2636,7 +2760,7 @@
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
       <c r="O6" s="13"/>
-      <c r="P6" s="14" t="s">
+      <c r="P6" s="28" t="s">
         <v>81</v>
       </c>
       <c r="Q6" s="13" t="s">
@@ -2653,7 +2777,7 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
       <c r="AB6" s="13"/>
-      <c r="AC6" s="14" t="s">
+      <c r="AC6" s="28" t="s">
         <v>81</v>
       </c>
       <c r="AD6" s="13" t="s">
@@ -2670,7 +2794,7 @@
       <c r="AM6" s="13"/>
       <c r="AN6" s="13"/>
       <c r="AO6" s="13"/>
-      <c r="AP6" s="14" t="s">
+      <c r="AP6" s="28" t="s">
         <v>81</v>
       </c>
       <c r="AQ6" s="13" t="s">
@@ -2687,7 +2811,7 @@
       <c r="AZ6" s="13"/>
       <c r="BA6" s="13"/>
       <c r="BB6" s="13"/>
-      <c r="BC6" s="14" t="s">
+      <c r="BC6" s="28" t="s">
         <v>81</v>
       </c>
       <c r="BD6" s="13" t="s">
@@ -2704,32 +2828,32 @@
       <c r="BM6" s="13"/>
       <c r="BN6" s="13"/>
       <c r="BO6" s="13"/>
-      <c r="BP6" s="14" t="s">
+      <c r="BP6" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="BQ6" s="15" t="s">
+      <c r="BQ6" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="BR6" s="16" t="s">
+      <c r="BR6" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="BS6" s="15" t="s">
+      <c r="BS6" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="BT6" s="16" t="s">
+      <c r="BT6" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="BU6" s="15" t="s">
+      <c r="BU6" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="BV6" s="15" t="s">
+      <c r="BV6" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="7" ht="129.75" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="93.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="16"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="17" t="s">
         <v>87</v>
       </c>
@@ -2766,7 +2890,7 @@
       <c r="O7" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="P7" s="14"/>
+      <c r="P7" s="28"/>
       <c r="Q7" s="17" t="s">
         <v>99</v>
       </c>
@@ -2803,7 +2927,7 @@
       <c r="AB7" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="AC7" s="14"/>
+      <c r="AC7" s="28"/>
       <c r="AD7" s="17" t="s">
         <v>111</v>
       </c>
@@ -2840,7 +2964,7 @@
       <c r="AO7" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="AP7" s="14"/>
+      <c r="AP7" s="28"/>
       <c r="AQ7" s="17" t="s">
         <v>123</v>
       </c>
@@ -2877,7 +3001,7 @@
       <c r="BB7" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="BC7" s="14"/>
+      <c r="BC7" s="28"/>
       <c r="BD7" s="17" t="s">
         <v>135</v>
       </c>
@@ -2914,15 +3038,15 @@
       <c r="BO7" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="14"/>
-      <c r="BQ7" s="15"/>
-      <c r="BR7" s="16"/>
-      <c r="BS7" s="15"/>
-      <c r="BT7" s="16"/>
-      <c r="BU7" s="15"/>
-      <c r="BV7" s="15"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BP7" s="28"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="27"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="27"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
         <v>147</v>
       </c>
@@ -2942,8 +3066,9 @@
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
       <c r="O8" s="19"/>
-      <c r="P8" s="20">
-        <f>SUM(D8:O8)</f>
+      <c r="P8" s="20" t="n">
+        <f aca="false">SUM(D8:O8)</f>
+        <v>0</v>
       </c>
       <c r="Q8" s="19"/>
       <c r="R8" s="19"/>
@@ -2957,8 +3082,9 @@
       <c r="Z8" s="19"/>
       <c r="AA8" s="19"/>
       <c r="AB8" s="19"/>
-      <c r="AC8" s="20">
-        <f>SUM(Q8:AB8)</f>
+      <c r="AC8" s="20" t="n">
+        <f aca="false">SUM(Q8:AB8)</f>
+        <v>0</v>
       </c>
       <c r="AD8" s="19"/>
       <c r="AE8" s="19"/>
@@ -2972,8 +3098,9 @@
       <c r="AM8" s="19"/>
       <c r="AN8" s="19"/>
       <c r="AO8" s="19"/>
-      <c r="AP8" s="20">
-        <f>SUM(AD8:AO8)</f>
+      <c r="AP8" s="20" t="n">
+        <f aca="false">SUM(AD8:AO8)</f>
+        <v>0</v>
       </c>
       <c r="AQ8" s="19"/>
       <c r="AR8" s="19"/>
@@ -2987,8 +3114,9 @@
       <c r="AZ8" s="19"/>
       <c r="BA8" s="19"/>
       <c r="BB8" s="19"/>
-      <c r="BC8" s="20">
-        <f>SUM(AQ8:BB8)</f>
+      <c r="BC8" s="20" t="n">
+        <f aca="false">SUM(AQ8:BB8)</f>
+        <v>0</v>
       </c>
       <c r="BD8" s="19"/>
       <c r="BE8" s="19"/>
@@ -3002,22 +3130,25 @@
       <c r="BM8" s="19"/>
       <c r="BN8" s="19"/>
       <c r="BO8" s="19"/>
-      <c r="BP8" s="20">
-        <f>SUM(BD8:BO8)</f>
-      </c>
-      <c r="BQ8" s="21">
-        <f>SUM(P8+AC8+AP8+BC8+BP8)</f>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="BP8" s="20" t="n">
+        <f aca="false">SUM(BD8:BO8)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ8" s="21" t="n">
+        <f aca="false">SUM(P8+AC8+AP8+BC8+BP8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="19">
-        <f>PLANTILLA_ETAPA_1!BQ9</f>
+      <c r="C9" s="19" t="n">
+        <f aca="false">PLANTILLA_ETAPA_1!BQ9</f>
+        <v>0</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
@@ -3031,8 +3162,9 @@
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9" s="19"/>
-      <c r="P9" s="24">
-        <f>SUM(D9:O9)</f>
+      <c r="P9" s="24" t="n">
+        <f aca="false">SUM(D9:O9)</f>
+        <v>0</v>
       </c>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
@@ -3046,8 +3178,9 @@
       <c r="Z9" s="19"/>
       <c r="AA9" s="19"/>
       <c r="AB9" s="19"/>
-      <c r="AC9" s="24">
-        <f>SUM(Q9:AB9)</f>
+      <c r="AC9" s="24" t="n">
+        <f aca="false">SUM(Q9:AB9)</f>
+        <v>0</v>
       </c>
       <c r="AD9" s="19"/>
       <c r="AE9" s="19"/>
@@ -3061,8 +3194,9 @@
       <c r="AM9" s="19"/>
       <c r="AN9" s="19"/>
       <c r="AO9" s="19"/>
-      <c r="AP9" s="24">
-        <f>SUM(AD9:AO9)</f>
+      <c r="AP9" s="24" t="n">
+        <f aca="false">SUM(AD9:AO9)</f>
+        <v>0</v>
       </c>
       <c r="AQ9" s="19"/>
       <c r="AR9" s="19"/>
@@ -3076,8 +3210,9 @@
       <c r="AZ9" s="19"/>
       <c r="BA9" s="19"/>
       <c r="BB9" s="19"/>
-      <c r="BC9" s="24">
-        <f>SUM(AQ9:BB9)</f>
+      <c r="BC9" s="24" t="n">
+        <f aca="false">SUM(AQ9:BB9)</f>
+        <v>0</v>
       </c>
       <c r="BD9" s="19"/>
       <c r="BE9" s="19"/>
@@ -3091,31 +3226,36 @@
       <c r="BM9" s="19"/>
       <c r="BN9" s="19"/>
       <c r="BO9" s="19"/>
-      <c r="BP9" s="24">
-        <f>SUM(BD9:BO9)</f>
-      </c>
-      <c r="BQ9" s="21">
-        <f>SUM(P9+AC9+AP9+BC9+BP9)</f>
+      <c r="BP9" s="24" t="n">
+        <f aca="false">SUM(BD9:BO9)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ9" s="21" t="n">
+        <f aca="false">SUM(P9+AC9+AP9+BC9+BP9)</f>
+        <v>0</v>
       </c>
       <c r="BR9" s="25"/>
-      <c r="BS9" s="19">
-        <f>SUM(C9+BR9)</f>
-      </c>
-      <c r="BT9" s="25">
-        <f>IF((C9+BR9)/2&lt;=1.5,1,IF(BR9=1,1,ROUND((C9+BR9)/2,0)))</f>
+      <c r="BS9" s="19" t="n">
+        <f aca="false">SUM(C9+BR9)</f>
+        <v>0</v>
+      </c>
+      <c r="BT9" s="25" t="n">
+        <f aca="false">IF((C9+BR9)/2&lt;=1.5,1,IF(BR9=1,1,ROUND((C9+BR9)/2,0)))</f>
+        <v>1</v>
       </c>
       <c r="BU9" s="19"/>
       <c r="BV9" s="19"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="n">
         <v>2</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="19">
-        <f>PLANTILLA_ETAPA_1!BQ10</f>
+      <c r="C10" s="19" t="n">
+        <f aca="false">PLANTILLA_ETAPA_1!BQ10</f>
+        <v>0</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -3129,8 +3269,9 @@
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
       <c r="O10" s="19"/>
-      <c r="P10" s="24">
-        <f>SUM(D10:O10)</f>
+      <c r="P10" s="24" t="n">
+        <f aca="false">SUM(D10:O10)</f>
+        <v>0</v>
       </c>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
@@ -3144,8 +3285,9 @@
       <c r="Z10" s="19"/>
       <c r="AA10" s="19"/>
       <c r="AB10" s="19"/>
-      <c r="AC10" s="24">
-        <f>SUM(Q10:AB10)</f>
+      <c r="AC10" s="24" t="n">
+        <f aca="false">SUM(Q10:AB10)</f>
+        <v>0</v>
       </c>
       <c r="AD10" s="19"/>
       <c r="AE10" s="19"/>
@@ -3159,8 +3301,9 @@
       <c r="AM10" s="19"/>
       <c r="AN10" s="19"/>
       <c r="AO10" s="19"/>
-      <c r="AP10" s="24">
-        <f>SUM(AD10:AO10)</f>
+      <c r="AP10" s="24" t="n">
+        <f aca="false">SUM(AD10:AO10)</f>
+        <v>0</v>
       </c>
       <c r="AQ10" s="19"/>
       <c r="AR10" s="19"/>
@@ -3174,8 +3317,9 @@
       <c r="AZ10" s="19"/>
       <c r="BA10" s="19"/>
       <c r="BB10" s="19"/>
-      <c r="BC10" s="24">
-        <f>SUM(AQ10:BB10)</f>
+      <c r="BC10" s="24" t="n">
+        <f aca="false">SUM(AQ10:BB10)</f>
+        <v>0</v>
       </c>
       <c r="BD10" s="19"/>
       <c r="BE10" s="19"/>
@@ -3189,31 +3333,36 @@
       <c r="BM10" s="19"/>
       <c r="BN10" s="19"/>
       <c r="BO10" s="19"/>
-      <c r="BP10" s="24">
-        <f>SUM(BD10:BO10)</f>
-      </c>
-      <c r="BQ10" s="21">
-        <f>SUM(P10+AC10+AP10+BC10+BP10)</f>
+      <c r="BP10" s="24" t="n">
+        <f aca="false">SUM(BD10:BO10)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ10" s="21" t="n">
+        <f aca="false">SUM(P10+AC10+AP10+BC10+BP10)</f>
+        <v>0</v>
       </c>
       <c r="BR10" s="25"/>
-      <c r="BS10" s="19">
-        <f>SUM(C10+BR10)</f>
-      </c>
-      <c r="BT10" s="25">
-        <f>IF((C10+BR10)/2&lt;=1.5,1,IF(BR10=1,1,ROUND((C10+BR10)/2,0)))</f>
+      <c r="BS10" s="19" t="n">
+        <f aca="false">SUM(C10+BR10)</f>
+        <v>0</v>
+      </c>
+      <c r="BT10" s="25" t="n">
+        <f aca="false">IF((C10+BR10)/2&lt;=1.5,1,IF(BR10=1,1,ROUND((C10+BR10)/2,0)))</f>
+        <v>1</v>
       </c>
       <c r="BU10" s="19"/>
       <c r="BV10" s="19"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="n">
         <v>3</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="19">
-        <f>PLANTILLA_ETAPA_1!BQ11</f>
+      <c r="C11" s="19" t="n">
+        <f aca="false">PLANTILLA_ETAPA_1!BQ11</f>
+        <v>0</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -3227,8 +3376,9 @@
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
       <c r="O11" s="19"/>
-      <c r="P11" s="24">
-        <f>SUM(D11:O11)</f>
+      <c r="P11" s="24" t="n">
+        <f aca="false">SUM(D11:O11)</f>
+        <v>0</v>
       </c>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
@@ -3242,8 +3392,9 @@
       <c r="Z11" s="19"/>
       <c r="AA11" s="19"/>
       <c r="AB11" s="19"/>
-      <c r="AC11" s="24">
-        <f>SUM(Q11:AB11)</f>
+      <c r="AC11" s="24" t="n">
+        <f aca="false">SUM(Q11:AB11)</f>
+        <v>0</v>
       </c>
       <c r="AD11" s="19"/>
       <c r="AE11" s="19"/>
@@ -3257,8 +3408,9 @@
       <c r="AM11" s="19"/>
       <c r="AN11" s="19"/>
       <c r="AO11" s="19"/>
-      <c r="AP11" s="24">
-        <f>SUM(AD11:AO11)</f>
+      <c r="AP11" s="24" t="n">
+        <f aca="false">SUM(AD11:AO11)</f>
+        <v>0</v>
       </c>
       <c r="AQ11" s="19"/>
       <c r="AR11" s="19"/>
@@ -3272,8 +3424,9 @@
       <c r="AZ11" s="19"/>
       <c r="BA11" s="19"/>
       <c r="BB11" s="19"/>
-      <c r="BC11" s="24">
-        <f>SUM(AQ11:BB11)</f>
+      <c r="BC11" s="24" t="n">
+        <f aca="false">SUM(AQ11:BB11)</f>
+        <v>0</v>
       </c>
       <c r="BD11" s="19"/>
       <c r="BE11" s="19"/>
@@ -3287,23 +3440,27 @@
       <c r="BM11" s="19"/>
       <c r="BN11" s="19"/>
       <c r="BO11" s="19"/>
-      <c r="BP11" s="24">
-        <f>SUM(BD11:BO11)</f>
-      </c>
-      <c r="BQ11" s="21">
-        <f>SUM(P11+AC11+AP11+BC11+BP11)</f>
+      <c r="BP11" s="24" t="n">
+        <f aca="false">SUM(BD11:BO11)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ11" s="21" t="n">
+        <f aca="false">SUM(P11+AC11+AP11+BC11+BP11)</f>
+        <v>0</v>
       </c>
       <c r="BR11" s="25"/>
-      <c r="BS11" s="19">
-        <f>SUM(C11+BR11)</f>
-      </c>
-      <c r="BT11" s="25">
-        <f>IF((C11+BR11)/2&lt;=1.5,1,IF(BR11=1,1,ROUND((C11+BR11)/2,0)))</f>
+      <c r="BS11" s="19" t="n">
+        <f aca="false">SUM(C11+BR11)</f>
+        <v>0</v>
+      </c>
+      <c r="BT11" s="25" t="n">
+        <f aca="false">IF((C11+BR11)/2&lt;=1.5,1,IF(BR11=1,1,ROUND((C11+BR11)/2,0)))</f>
+        <v>1</v>
       </c>
       <c r="BU11" s="19"/>
       <c r="BV11" s="19"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3386,18 +3543,18 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:R5"/>
     <mergeCell ref="T5:V5"/>
-    <mergeCell ref="D6:O6"/>
-    <mergeCell ref="Q6:AB6"/>
-    <mergeCell ref="AD6:AO6"/>
-    <mergeCell ref="AQ6:BB6"/>
-    <mergeCell ref="BD6:BO6"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:O6"/>
     <mergeCell ref="P6:P7"/>
+    <mergeCell ref="Q6:AB6"/>
     <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="AD6:AO6"/>
     <mergeCell ref="AP6:AP7"/>
+    <mergeCell ref="AQ6:BB6"/>
     <mergeCell ref="BC6:BC7"/>
+    <mergeCell ref="BD6:BO6"/>
     <mergeCell ref="BP6:BP7"/>
     <mergeCell ref="BQ6:BQ7"/>
     <mergeCell ref="BR6:BR7"/>
@@ -3407,7 +3564,12 @@
     <mergeCell ref="BV6:BV7"/>
     <mergeCell ref="BI15:BQ15"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/backend/src/main/resources/templates/PLANTILLA_PLANILLA_PROCESO_CTN.xlsx
+++ b/backend/src/main/resources/templates/PLANTILLA_PLANILLA_PROCESO_CTN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LEYENDA_PARA_DESARROLLO" sheetId="1" state="visible" r:id="rId3"/>
@@ -690,124 +690,128 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -820,47 +824,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4DFEC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF2E5395"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD8E4BC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1104,362 +1067,362 @@
   <dimension ref="A1:B50"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="3" style="0" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="3" style="1" width="13.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="2"/>
+      <c r="B34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="2"/>
+      <c r="B44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1482,981 +1445,981 @@
   <dimension ref="A1:BQ16"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="16" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="29" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="42" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="55" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="67" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="16" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="29" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="42" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="55" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="67" style="1" width="9.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="5"/>
+      <c r="AX1" s="5"/>
+      <c r="AY1" s="5"/>
+      <c r="AZ1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6"/>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6"/>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="6"/>
-      <c r="AO3" s="6"/>
-      <c r="AP3" s="6"/>
-      <c r="AQ3" s="6"/>
-      <c r="AR3" s="6"/>
-      <c r="AS3" s="6"/>
-      <c r="AT3" s="6"/>
-      <c r="AU3" s="6"/>
-      <c r="AV3" s="6"/>
-      <c r="AW3" s="6"/>
-      <c r="AX3" s="6"/>
-      <c r="AY3" s="6"/>
-      <c r="AZ3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="7"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="7"/>
+      <c r="AN3" s="7"/>
+      <c r="AO3" s="7"/>
+      <c r="AP3" s="7"/>
+      <c r="AQ3" s="7"/>
+      <c r="AR3" s="7"/>
+      <c r="AS3" s="7"/>
+      <c r="AT3" s="7"/>
+      <c r="AU3" s="7"/>
+      <c r="AV3" s="7"/>
+      <c r="AW3" s="7"/>
+      <c r="AX3" s="7"/>
+      <c r="AY3" s="7"/>
+      <c r="AZ3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="8" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="14" t="s">
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="AC6" s="13" t="s">
+      <c r="AC6" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="14" t="s">
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="14"/>
+      <c r="AN6" s="14"/>
+      <c r="AO6" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="AP6" s="13" t="s">
+      <c r="AP6" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="14" t="s">
+      <c r="AQ6" s="14"/>
+      <c r="AR6" s="14"/>
+      <c r="AS6" s="14"/>
+      <c r="AT6" s="14"/>
+      <c r="AU6" s="14"/>
+      <c r="AV6" s="14"/>
+      <c r="AW6" s="14"/>
+      <c r="AX6" s="14"/>
+      <c r="AY6" s="14"/>
+      <c r="AZ6" s="14"/>
+      <c r="BA6" s="14"/>
+      <c r="BB6" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="BC6" s="13" t="s">
+      <c r="BC6" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="BD6" s="13"/>
-      <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="13"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="13"/>
-      <c r="BJ6" s="13"/>
-      <c r="BK6" s="13"/>
-      <c r="BL6" s="13"/>
-      <c r="BM6" s="13"/>
-      <c r="BN6" s="13"/>
-      <c r="BO6" s="14" t="s">
+      <c r="BD6" s="14"/>
+      <c r="BE6" s="14"/>
+      <c r="BF6" s="14"/>
+      <c r="BG6" s="14"/>
+      <c r="BH6" s="14"/>
+      <c r="BI6" s="14"/>
+      <c r="BJ6" s="14"/>
+      <c r="BK6" s="14"/>
+      <c r="BL6" s="14"/>
+      <c r="BM6" s="14"/>
+      <c r="BN6" s="14"/>
+      <c r="BO6" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="BP6" s="15" t="s">
+      <c r="BP6" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="BQ6" s="16" t="s">
+      <c r="BQ6" s="17" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="92.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="17" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="17" t="s">
+      <c r="O7" s="15"/>
+      <c r="P7" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="R7" s="17" t="s">
+      <c r="R7" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="S7" s="17" t="s">
+      <c r="S7" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="T7" s="17" t="s">
+      <c r="T7" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="U7" s="17" t="s">
+      <c r="U7" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="V7" s="17" t="s">
+      <c r="V7" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="W7" s="17" t="s">
+      <c r="W7" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="X7" s="17" t="s">
+      <c r="X7" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="Y7" s="17" t="s">
+      <c r="Y7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="Z7" s="17" t="s">
+      <c r="Z7" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="AA7" s="17" t="s">
+      <c r="AA7" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="17" t="s">
+      <c r="AB7" s="15"/>
+      <c r="AC7" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="AD7" s="17" t="s">
+      <c r="AD7" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="AE7" s="17" t="s">
+      <c r="AE7" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="AF7" s="17" t="s">
+      <c r="AF7" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="AG7" s="17" t="s">
+      <c r="AG7" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="AH7" s="17" t="s">
+      <c r="AH7" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="AI7" s="17" t="s">
+      <c r="AI7" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="AJ7" s="17" t="s">
+      <c r="AJ7" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="AK7" s="17" t="s">
+      <c r="AK7" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="AL7" s="17" t="s">
+      <c r="AL7" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="AM7" s="17" t="s">
+      <c r="AM7" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="AN7" s="17" t="s">
+      <c r="AN7" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="AO7" s="14"/>
-      <c r="AP7" s="17" t="s">
+      <c r="AO7" s="15"/>
+      <c r="AP7" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="AQ7" s="17" t="s">
+      <c r="AQ7" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="AR7" s="17" t="s">
+      <c r="AR7" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="AS7" s="17" t="s">
+      <c r="AS7" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="AT7" s="17" t="s">
+      <c r="AT7" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="AU7" s="17" t="s">
+      <c r="AU7" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="AV7" s="17" t="s">
+      <c r="AV7" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="AW7" s="17" t="s">
+      <c r="AW7" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="AX7" s="17" t="s">
+      <c r="AX7" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="AY7" s="17" t="s">
+      <c r="AY7" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="AZ7" s="17" t="s">
+      <c r="AZ7" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="BA7" s="17" t="s">
+      <c r="BA7" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="BB7" s="14"/>
-      <c r="BC7" s="17" t="s">
+      <c r="BB7" s="15"/>
+      <c r="BC7" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="BD7" s="17" t="s">
+      <c r="BD7" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="BE7" s="17" t="s">
+      <c r="BE7" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BF7" s="17" t="s">
+      <c r="BF7" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="BG7" s="17" t="s">
+      <c r="BG7" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="BH7" s="17" t="s">
+      <c r="BH7" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="BI7" s="17" t="s">
+      <c r="BI7" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="BJ7" s="17" t="s">
+      <c r="BJ7" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="BK7" s="17" t="s">
+      <c r="BK7" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="BL7" s="17" t="s">
+      <c r="BL7" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="BM7" s="17" t="s">
+      <c r="BM7" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="BN7" s="17" t="s">
+      <c r="BN7" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="BO7" s="14"/>
-      <c r="BP7" s="15"/>
-      <c r="BQ7" s="16"/>
+      <c r="BO7" s="15"/>
+      <c r="BP7" s="16"/>
+      <c r="BQ7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="20" t="n">
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="21" t="n">
         <f aca="false">SUM(C8:N8)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="20" t="n">
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="21" t="n">
         <f aca="false">SUM(P8:AA8)</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="19"/>
-      <c r="AG8" s="19"/>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="19"/>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="20" t="n">
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="20"/>
+      <c r="AI8" s="20"/>
+      <c r="AJ8" s="20"/>
+      <c r="AK8" s="20"/>
+      <c r="AL8" s="20"/>
+      <c r="AM8" s="20"/>
+      <c r="AN8" s="20"/>
+      <c r="AO8" s="21" t="n">
         <f aca="false">SUM(AC8:AN8)</f>
         <v>0</v>
       </c>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="19"/>
-      <c r="AT8" s="19"/>
-      <c r="AU8" s="19"/>
-      <c r="AV8" s="19"/>
-      <c r="AW8" s="19"/>
-      <c r="AX8" s="19"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="19"/>
-      <c r="BA8" s="19"/>
-      <c r="BB8" s="20" t="n">
+      <c r="AP8" s="20"/>
+      <c r="AQ8" s="20"/>
+      <c r="AR8" s="20"/>
+      <c r="AS8" s="20"/>
+      <c r="AT8" s="20"/>
+      <c r="AU8" s="20"/>
+      <c r="AV8" s="20"/>
+      <c r="AW8" s="20"/>
+      <c r="AX8" s="20"/>
+      <c r="AY8" s="20"/>
+      <c r="AZ8" s="20"/>
+      <c r="BA8" s="20"/>
+      <c r="BB8" s="21" t="n">
         <f aca="false">SUM(AP8:BA8)</f>
         <v>0</v>
       </c>
-      <c r="BC8" s="19"/>
-      <c r="BD8" s="19"/>
-      <c r="BE8" s="19"/>
-      <c r="BF8" s="19"/>
-      <c r="BG8" s="19"/>
-      <c r="BH8" s="19"/>
-      <c r="BI8" s="19"/>
-      <c r="BJ8" s="19"/>
-      <c r="BK8" s="19"/>
-      <c r="BL8" s="19"/>
-      <c r="BM8" s="19"/>
-      <c r="BN8" s="19"/>
-      <c r="BO8" s="20" t="n">
+      <c r="BC8" s="20"/>
+      <c r="BD8" s="20"/>
+      <c r="BE8" s="20"/>
+      <c r="BF8" s="20"/>
+      <c r="BG8" s="20"/>
+      <c r="BH8" s="20"/>
+      <c r="BI8" s="20"/>
+      <c r="BJ8" s="20"/>
+      <c r="BK8" s="20"/>
+      <c r="BL8" s="20"/>
+      <c r="BM8" s="20"/>
+      <c r="BN8" s="20"/>
+      <c r="BO8" s="21" t="n">
         <f aca="false">SUM(BC8:BN8)</f>
         <v>0</v>
       </c>
-      <c r="BP8" s="21" t="n">
+      <c r="BP8" s="22" t="n">
         <f aca="false">SUM(O8+AB8+AO8+BB8+BO8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="24" t="n">
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="25" t="n">
         <f aca="false">SUM(C9:N9)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="24" t="n">
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="25" t="n">
         <f aca="false">SUM(P9:AA9)</f>
         <v>0</v>
       </c>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="24" t="n">
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="20"/>
+      <c r="AJ9" s="20"/>
+      <c r="AK9" s="20"/>
+      <c r="AL9" s="20"/>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="20"/>
+      <c r="AO9" s="25" t="n">
         <f aca="false">SUM(AC9:AN9)</f>
         <v>0</v>
       </c>
-      <c r="AP9" s="19"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="19"/>
-      <c r="AV9" s="19"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="19"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="19"/>
-      <c r="BB9" s="24" t="n">
+      <c r="AP9" s="20"/>
+      <c r="AQ9" s="20"/>
+      <c r="AR9" s="20"/>
+      <c r="AS9" s="20"/>
+      <c r="AT9" s="20"/>
+      <c r="AU9" s="20"/>
+      <c r="AV9" s="20"/>
+      <c r="AW9" s="20"/>
+      <c r="AX9" s="20"/>
+      <c r="AY9" s="20"/>
+      <c r="AZ9" s="20"/>
+      <c r="BA9" s="20"/>
+      <c r="BB9" s="25" t="n">
         <f aca="false">SUM(AP9:BA9)</f>
         <v>0</v>
       </c>
-      <c r="BC9" s="19"/>
-      <c r="BD9" s="19"/>
-      <c r="BE9" s="19"/>
-      <c r="BF9" s="19"/>
-      <c r="BG9" s="19"/>
-      <c r="BH9" s="19"/>
-      <c r="BI9" s="19"/>
-      <c r="BJ9" s="19"/>
-      <c r="BK9" s="19"/>
-      <c r="BL9" s="19"/>
-      <c r="BM9" s="19"/>
-      <c r="BN9" s="19"/>
-      <c r="BO9" s="24" t="n">
+      <c r="BC9" s="20"/>
+      <c r="BD9" s="20"/>
+      <c r="BE9" s="20"/>
+      <c r="BF9" s="20"/>
+      <c r="BG9" s="20"/>
+      <c r="BH9" s="20"/>
+      <c r="BI9" s="20"/>
+      <c r="BJ9" s="20"/>
+      <c r="BK9" s="20"/>
+      <c r="BL9" s="20"/>
+      <c r="BM9" s="20"/>
+      <c r="BN9" s="20"/>
+      <c r="BO9" s="25" t="n">
         <f aca="false">SUM(BC9:BN9)</f>
         <v>0</v>
       </c>
-      <c r="BP9" s="21" t="n">
+      <c r="BP9" s="22" t="n">
         <f aca="false">SUM(O9+AB9+AO9+BB9+BO9)</f>
         <v>0</v>
       </c>
-      <c r="BQ9" s="25"/>
+      <c r="BQ9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="24" t="n">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="25" t="n">
         <f aca="false">SUM(C10:N10)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="24" t="n">
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="25" t="n">
         <f aca="false">SUM(P10:AA10)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="19"/>
-      <c r="AG10" s="19"/>
-      <c r="AH10" s="19"/>
-      <c r="AI10" s="19"/>
-      <c r="AJ10" s="19"/>
-      <c r="AK10" s="19"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="19"/>
-      <c r="AN10" s="19"/>
-      <c r="AO10" s="24" t="n">
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="20"/>
+      <c r="AK10" s="20"/>
+      <c r="AL10" s="20"/>
+      <c r="AM10" s="20"/>
+      <c r="AN10" s="20"/>
+      <c r="AO10" s="25" t="n">
         <f aca="false">SUM(AC10:AN10)</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="19"/>
-      <c r="AQ10" s="19"/>
-      <c r="AR10" s="19"/>
-      <c r="AS10" s="19"/>
-      <c r="AT10" s="19"/>
-      <c r="AU10" s="19"/>
-      <c r="AV10" s="19"/>
-      <c r="AW10" s="19"/>
-      <c r="AX10" s="19"/>
-      <c r="AY10" s="19"/>
-      <c r="AZ10" s="19"/>
-      <c r="BA10" s="19"/>
-      <c r="BB10" s="24" t="n">
+      <c r="AP10" s="20"/>
+      <c r="AQ10" s="20"/>
+      <c r="AR10" s="20"/>
+      <c r="AS10" s="20"/>
+      <c r="AT10" s="20"/>
+      <c r="AU10" s="20"/>
+      <c r="AV10" s="20"/>
+      <c r="AW10" s="20"/>
+      <c r="AX10" s="20"/>
+      <c r="AY10" s="20"/>
+      <c r="AZ10" s="20"/>
+      <c r="BA10" s="20"/>
+      <c r="BB10" s="25" t="n">
         <f aca="false">SUM(AP10:BA10)</f>
         <v>0</v>
       </c>
-      <c r="BC10" s="19"/>
-      <c r="BD10" s="19"/>
-      <c r="BE10" s="19"/>
-      <c r="BF10" s="19"/>
-      <c r="BG10" s="19"/>
-      <c r="BH10" s="19"/>
-      <c r="BI10" s="19"/>
-      <c r="BJ10" s="19"/>
-      <c r="BK10" s="19"/>
-      <c r="BL10" s="19"/>
-      <c r="BM10" s="19"/>
-      <c r="BN10" s="19"/>
-      <c r="BO10" s="24" t="n">
+      <c r="BC10" s="20"/>
+      <c r="BD10" s="20"/>
+      <c r="BE10" s="20"/>
+      <c r="BF10" s="20"/>
+      <c r="BG10" s="20"/>
+      <c r="BH10" s="20"/>
+      <c r="BI10" s="20"/>
+      <c r="BJ10" s="20"/>
+      <c r="BK10" s="20"/>
+      <c r="BL10" s="20"/>
+      <c r="BM10" s="20"/>
+      <c r="BN10" s="20"/>
+      <c r="BO10" s="25" t="n">
         <f aca="false">SUM(BC10:BN10)</f>
         <v>0</v>
       </c>
-      <c r="BP10" s="21" t="n">
+      <c r="BP10" s="22" t="n">
         <f aca="false">SUM(O10+AB10+AO10+BB10+BO10)</f>
         <v>0</v>
       </c>
-      <c r="BQ10" s="25"/>
+      <c r="BQ10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="24" t="n">
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="25" t="n">
         <f aca="false">SUM(C11:N11)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="24" t="n">
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="25" t="n">
         <f aca="false">SUM(P11:AA11)</f>
         <v>0</v>
       </c>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="24" t="n">
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20"/>
+      <c r="AJ11" s="20"/>
+      <c r="AK11" s="20"/>
+      <c r="AL11" s="20"/>
+      <c r="AM11" s="20"/>
+      <c r="AN11" s="20"/>
+      <c r="AO11" s="25" t="n">
         <f aca="false">SUM(AC11:AN11)</f>
         <v>0</v>
       </c>
-      <c r="AP11" s="19"/>
-      <c r="AQ11" s="19"/>
-      <c r="AR11" s="19"/>
-      <c r="AS11" s="19"/>
-      <c r="AT11" s="19"/>
-      <c r="AU11" s="19"/>
-      <c r="AV11" s="19"/>
-      <c r="AW11" s="19"/>
-      <c r="AX11" s="19"/>
-      <c r="AY11" s="19"/>
-      <c r="AZ11" s="19"/>
-      <c r="BA11" s="19"/>
-      <c r="BB11" s="24" t="n">
+      <c r="AP11" s="20"/>
+      <c r="AQ11" s="20"/>
+      <c r="AR11" s="20"/>
+      <c r="AS11" s="20"/>
+      <c r="AT11" s="20"/>
+      <c r="AU11" s="20"/>
+      <c r="AV11" s="20"/>
+      <c r="AW11" s="20"/>
+      <c r="AX11" s="20"/>
+      <c r="AY11" s="20"/>
+      <c r="AZ11" s="20"/>
+      <c r="BA11" s="20"/>
+      <c r="BB11" s="25" t="n">
         <f aca="false">SUM(AP11:BA11)</f>
         <v>0</v>
       </c>
-      <c r="BC11" s="19"/>
-      <c r="BD11" s="19"/>
-      <c r="BE11" s="19"/>
-      <c r="BF11" s="19"/>
-      <c r="BG11" s="19"/>
-      <c r="BH11" s="19"/>
-      <c r="BI11" s="19"/>
-      <c r="BJ11" s="19"/>
-      <c r="BK11" s="19"/>
-      <c r="BL11" s="19"/>
-      <c r="BM11" s="19"/>
-      <c r="BN11" s="19"/>
-      <c r="BO11" s="24" t="n">
+      <c r="BC11" s="20"/>
+      <c r="BD11" s="20"/>
+      <c r="BE11" s="20"/>
+      <c r="BF11" s="20"/>
+      <c r="BG11" s="20"/>
+      <c r="BH11" s="20"/>
+      <c r="BI11" s="20"/>
+      <c r="BJ11" s="20"/>
+      <c r="BK11" s="20"/>
+      <c r="BL11" s="20"/>
+      <c r="BM11" s="20"/>
+      <c r="BN11" s="20"/>
+      <c r="BO11" s="25" t="n">
         <f aca="false">SUM(BC11:BN11)</f>
         <v>0</v>
       </c>
-      <c r="BP11" s="21" t="n">
+      <c r="BP11" s="22" t="n">
         <f aca="false">SUM(O11+AB11+AO11+BB11+BO11)</f>
         <v>0</v>
       </c>
-      <c r="BQ11" s="25"/>
+      <c r="BQ11" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="11"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="11"/>
-      <c r="AJ15" s="11"/>
-      <c r="AK15" s="11"/>
-      <c r="AL15" s="11"/>
-      <c r="AM15" s="11"/>
-      <c r="AN15" s="11"/>
-      <c r="AO15" s="11"/>
-      <c r="AP15" s="11"/>
-      <c r="AQ15" s="11"/>
-      <c r="AR15" s="11"/>
-      <c r="AS15" s="11"/>
-      <c r="AT15" s="11"/>
-      <c r="AU15" s="11"/>
-      <c r="AV15" s="11"/>
-      <c r="AW15" s="11"/>
-      <c r="AX15" s="11"/>
-      <c r="AY15" s="11"/>
-      <c r="AZ15" s="11"/>
-      <c r="BA15" s="11"/>
-      <c r="BB15" s="11"/>
-      <c r="BC15" s="11"/>
-      <c r="BD15" s="11"/>
-      <c r="BE15" s="11"/>
-      <c r="BF15" s="11"/>
-      <c r="BG15" s="11"/>
-      <c r="BH15" s="10" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="12"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="12"/>
+      <c r="AE15" s="12"/>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="BI15" s="10"/>
-      <c r="BJ15" s="10"/>
-      <c r="BK15" s="10"/>
-      <c r="BL15" s="10"/>
-      <c r="BM15" s="10"/>
-      <c r="BN15" s="10"/>
-      <c r="BO15" s="10"/>
-      <c r="BP15" s="10"/>
+      <c r="BI15" s="11"/>
+      <c r="BJ15" s="11"/>
+      <c r="BK15" s="11"/>
+      <c r="BL15" s="11"/>
+      <c r="BM15" s="11"/>
+      <c r="BN15" s="11"/>
+      <c r="BO15" s="11"/>
+      <c r="BP15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BH16" s="26"/>
-      <c r="BI16" s="26"/>
-      <c r="BJ16" s="26"/>
-      <c r="BK16" s="26"/>
-      <c r="BL16" s="26"/>
-      <c r="BM16" s="26"/>
-      <c r="BN16" s="26"/>
-      <c r="BO16" s="26"/>
-      <c r="BP16" s="26"/>
+      <c r="BH16" s="27"/>
+      <c r="BI16" s="27"/>
+      <c r="BJ16" s="27"/>
+      <c r="BK16" s="27"/>
+      <c r="BL16" s="27"/>
+      <c r="BM16" s="27"/>
+      <c r="BN16" s="27"/>
+      <c r="BO16" s="27"/>
+      <c r="BP16" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2503,1035 +2466,1035 @@
   <dimension ref="A1:BV15"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="17" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="30" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="43" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="0" width="9.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="56" style="0" width="5.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="68" style="0" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="17" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="30" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="43" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="56" style="1" width="5.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="68" style="1" width="9.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="5"/>
+      <c r="AX1" s="5"/>
+      <c r="AY1" s="5"/>
+      <c r="AZ1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6"/>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6"/>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="6"/>
-      <c r="AO3" s="6"/>
-      <c r="AP3" s="6"/>
-      <c r="AQ3" s="6"/>
-      <c r="AR3" s="6"/>
-      <c r="AS3" s="6"/>
-      <c r="AT3" s="6"/>
-      <c r="AU3" s="6"/>
-      <c r="AV3" s="6"/>
-      <c r="AW3" s="6"/>
-      <c r="AX3" s="6"/>
-      <c r="AY3" s="6"/>
-      <c r="AZ3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="7"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="7"/>
+      <c r="AN3" s="7"/>
+      <c r="AO3" s="7"/>
+      <c r="AP3" s="7"/>
+      <c r="AQ3" s="7"/>
+      <c r="AR3" s="7"/>
+      <c r="AS3" s="7"/>
+      <c r="AT3" s="7"/>
+      <c r="AU3" s="7"/>
+      <c r="AV3" s="7"/>
+      <c r="AW3" s="7"/>
+      <c r="AX3" s="7"/>
+      <c r="AY3" s="7"/>
+      <c r="AZ3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="8" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="28" t="s">
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="Q6" s="13" t="s">
+      <c r="Q6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="28" t="s">
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="AD6" s="13" t="s">
+      <c r="AD6" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="13"/>
-      <c r="AP6" s="28" t="s">
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="14"/>
+      <c r="AN6" s="14"/>
+      <c r="AO6" s="14"/>
+      <c r="AP6" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="AQ6" s="13" t="s">
+      <c r="AQ6" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="13"/>
-      <c r="BC6" s="28" t="s">
+      <c r="AR6" s="14"/>
+      <c r="AS6" s="14"/>
+      <c r="AT6" s="14"/>
+      <c r="AU6" s="14"/>
+      <c r="AV6" s="14"/>
+      <c r="AW6" s="14"/>
+      <c r="AX6" s="14"/>
+      <c r="AY6" s="14"/>
+      <c r="AZ6" s="14"/>
+      <c r="BA6" s="14"/>
+      <c r="BB6" s="14"/>
+      <c r="BC6" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="BD6" s="13" t="s">
+      <c r="BD6" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="13"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="13"/>
-      <c r="BJ6" s="13"/>
-      <c r="BK6" s="13"/>
-      <c r="BL6" s="13"/>
-      <c r="BM6" s="13"/>
-      <c r="BN6" s="13"/>
-      <c r="BO6" s="13"/>
-      <c r="BP6" s="28" t="s">
+      <c r="BE6" s="14"/>
+      <c r="BF6" s="14"/>
+      <c r="BG6" s="14"/>
+      <c r="BH6" s="14"/>
+      <c r="BI6" s="14"/>
+      <c r="BJ6" s="14"/>
+      <c r="BK6" s="14"/>
+      <c r="BL6" s="14"/>
+      <c r="BM6" s="14"/>
+      <c r="BN6" s="14"/>
+      <c r="BO6" s="14"/>
+      <c r="BP6" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="BQ6" s="29" t="s">
+      <c r="BQ6" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="BR6" s="27" t="s">
+      <c r="BR6" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="BS6" s="29" t="s">
+      <c r="BS6" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="BT6" s="27" t="s">
+      <c r="BT6" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="BU6" s="29" t="s">
+      <c r="BU6" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="BV6" s="29" t="s">
+      <c r="BV6" s="30" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="93.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="17" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="O7" s="17" t="s">
+      <c r="O7" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="17" t="s">
+      <c r="P7" s="29"/>
+      <c r="Q7" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="R7" s="17" t="s">
+      <c r="R7" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="S7" s="17" t="s">
+      <c r="S7" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="T7" s="17" t="s">
+      <c r="T7" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="U7" s="17" t="s">
+      <c r="U7" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="V7" s="17" t="s">
+      <c r="V7" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="W7" s="17" t="s">
+      <c r="W7" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="X7" s="17" t="s">
+      <c r="X7" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="Y7" s="17" t="s">
+      <c r="Y7" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="Z7" s="17" t="s">
+      <c r="Z7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="AA7" s="17" t="s">
+      <c r="AA7" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="AB7" s="17" t="s">
+      <c r="AB7" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="17" t="s">
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="AE7" s="17" t="s">
+      <c r="AE7" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="AF7" s="17" t="s">
+      <c r="AF7" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="AG7" s="17" t="s">
+      <c r="AG7" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="AH7" s="17" t="s">
+      <c r="AH7" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="AI7" s="17" t="s">
+      <c r="AI7" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="AJ7" s="17" t="s">
+      <c r="AJ7" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="AK7" s="17" t="s">
+      <c r="AK7" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="AL7" s="17" t="s">
+      <c r="AL7" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="AM7" s="17" t="s">
+      <c r="AM7" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="AN7" s="17" t="s">
+      <c r="AN7" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="AO7" s="17" t="s">
+      <c r="AO7" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="AP7" s="28"/>
-      <c r="AQ7" s="17" t="s">
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="AR7" s="17" t="s">
+      <c r="AR7" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="AS7" s="17" t="s">
+      <c r="AS7" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="AT7" s="17" t="s">
+      <c r="AT7" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="AU7" s="17" t="s">
+      <c r="AU7" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="AV7" s="17" t="s">
+      <c r="AV7" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="AW7" s="17" t="s">
+      <c r="AW7" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="AX7" s="17" t="s">
+      <c r="AX7" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="AY7" s="17" t="s">
+      <c r="AY7" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="AZ7" s="17" t="s">
+      <c r="AZ7" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="BA7" s="17" t="s">
+      <c r="BA7" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="BB7" s="17" t="s">
+      <c r="BB7" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="BC7" s="28"/>
-      <c r="BD7" s="17" t="s">
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="BE7" s="17" t="s">
+      <c r="BE7" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="BF7" s="17" t="s">
+      <c r="BF7" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BG7" s="17" t="s">
+      <c r="BG7" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="BH7" s="17" t="s">
+      <c r="BH7" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="BI7" s="17" t="s">
+      <c r="BI7" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="BJ7" s="17" t="s">
+      <c r="BJ7" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="BK7" s="17" t="s">
+      <c r="BK7" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="BL7" s="17" t="s">
+      <c r="BL7" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="BM7" s="17" t="s">
+      <c r="BM7" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="BN7" s="17" t="s">
+      <c r="BN7" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="BO7" s="17" t="s">
+      <c r="BO7" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="28"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="27"/>
-      <c r="BS7" s="29"/>
-      <c r="BT7" s="27"/>
-      <c r="BU7" s="29"/>
-      <c r="BV7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="30"/>
+      <c r="BR7" s="28"/>
+      <c r="BS7" s="30"/>
+      <c r="BT7" s="28"/>
+      <c r="BU7" s="30"/>
+      <c r="BV7" s="30"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="20" t="n">
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="21" t="n">
         <f aca="false">SUM(D8:O8)</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
-      <c r="AC8" s="20" t="n">
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21" t="n">
         <f aca="false">SUM(Q8:AB8)</f>
         <v>0</v>
       </c>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="19"/>
-      <c r="AG8" s="19"/>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="19"/>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="20" t="n">
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="20"/>
+      <c r="AI8" s="20"/>
+      <c r="AJ8" s="20"/>
+      <c r="AK8" s="20"/>
+      <c r="AL8" s="20"/>
+      <c r="AM8" s="20"/>
+      <c r="AN8" s="20"/>
+      <c r="AO8" s="20"/>
+      <c r="AP8" s="21" t="n">
         <f aca="false">SUM(AD8:AO8)</f>
         <v>0</v>
       </c>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="19"/>
-      <c r="AT8" s="19"/>
-      <c r="AU8" s="19"/>
-      <c r="AV8" s="19"/>
-      <c r="AW8" s="19"/>
-      <c r="AX8" s="19"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="19"/>
-      <c r="BA8" s="19"/>
-      <c r="BB8" s="19"/>
-      <c r="BC8" s="20" t="n">
+      <c r="AQ8" s="20"/>
+      <c r="AR8" s="20"/>
+      <c r="AS8" s="20"/>
+      <c r="AT8" s="20"/>
+      <c r="AU8" s="20"/>
+      <c r="AV8" s="20"/>
+      <c r="AW8" s="20"/>
+      <c r="AX8" s="20"/>
+      <c r="AY8" s="20"/>
+      <c r="AZ8" s="20"/>
+      <c r="BA8" s="20"/>
+      <c r="BB8" s="20"/>
+      <c r="BC8" s="21" t="n">
         <f aca="false">SUM(AQ8:BB8)</f>
         <v>0</v>
       </c>
-      <c r="BD8" s="19"/>
-      <c r="BE8" s="19"/>
-      <c r="BF8" s="19"/>
-      <c r="BG8" s="19"/>
-      <c r="BH8" s="19"/>
-      <c r="BI8" s="19"/>
-      <c r="BJ8" s="19"/>
-      <c r="BK8" s="19"/>
-      <c r="BL8" s="19"/>
-      <c r="BM8" s="19"/>
-      <c r="BN8" s="19"/>
-      <c r="BO8" s="19"/>
-      <c r="BP8" s="20" t="n">
+      <c r="BD8" s="20"/>
+      <c r="BE8" s="20"/>
+      <c r="BF8" s="20"/>
+      <c r="BG8" s="20"/>
+      <c r="BH8" s="20"/>
+      <c r="BI8" s="20"/>
+      <c r="BJ8" s="20"/>
+      <c r="BK8" s="20"/>
+      <c r="BL8" s="20"/>
+      <c r="BM8" s="20"/>
+      <c r="BN8" s="20"/>
+      <c r="BO8" s="20"/>
+      <c r="BP8" s="21" t="n">
         <f aca="false">SUM(BD8:BO8)</f>
         <v>0</v>
       </c>
-      <c r="BQ8" s="21" t="n">
+      <c r="BQ8" s="22" t="n">
         <f aca="false">SUM(P8+AC8+AP8+BC8+BP8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="20" t="n">
         <f aca="false">PLANTILLA_ETAPA_1!BQ9</f>
         <v>0</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="24" t="n">
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="25" t="n">
         <f aca="false">SUM(D9:O9)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="24" t="n">
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="25" t="n">
         <f aca="false">SUM(Q9:AB9)</f>
         <v>0</v>
       </c>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="24" t="n">
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="20"/>
+      <c r="AJ9" s="20"/>
+      <c r="AK9" s="20"/>
+      <c r="AL9" s="20"/>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="20"/>
+      <c r="AO9" s="20"/>
+      <c r="AP9" s="25" t="n">
         <f aca="false">SUM(AD9:AO9)</f>
         <v>0</v>
       </c>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="19"/>
-      <c r="AV9" s="19"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="19"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="19"/>
-      <c r="BB9" s="19"/>
-      <c r="BC9" s="24" t="n">
+      <c r="AQ9" s="20"/>
+      <c r="AR9" s="20"/>
+      <c r="AS9" s="20"/>
+      <c r="AT9" s="20"/>
+      <c r="AU9" s="20"/>
+      <c r="AV9" s="20"/>
+      <c r="AW9" s="20"/>
+      <c r="AX9" s="20"/>
+      <c r="AY9" s="20"/>
+      <c r="AZ9" s="20"/>
+      <c r="BA9" s="20"/>
+      <c r="BB9" s="20"/>
+      <c r="BC9" s="25" t="n">
         <f aca="false">SUM(AQ9:BB9)</f>
         <v>0</v>
       </c>
-      <c r="BD9" s="19"/>
-      <c r="BE9" s="19"/>
-      <c r="BF9" s="19"/>
-      <c r="BG9" s="19"/>
-      <c r="BH9" s="19"/>
-      <c r="BI9" s="19"/>
-      <c r="BJ9" s="19"/>
-      <c r="BK9" s="19"/>
-      <c r="BL9" s="19"/>
-      <c r="BM9" s="19"/>
-      <c r="BN9" s="19"/>
-      <c r="BO9" s="19"/>
-      <c r="BP9" s="24" t="n">
+      <c r="BD9" s="20"/>
+      <c r="BE9" s="20"/>
+      <c r="BF9" s="20"/>
+      <c r="BG9" s="20"/>
+      <c r="BH9" s="20"/>
+      <c r="BI9" s="20"/>
+      <c r="BJ9" s="20"/>
+      <c r="BK9" s="20"/>
+      <c r="BL9" s="20"/>
+      <c r="BM9" s="20"/>
+      <c r="BN9" s="20"/>
+      <c r="BO9" s="20"/>
+      <c r="BP9" s="25" t="n">
         <f aca="false">SUM(BD9:BO9)</f>
         <v>0</v>
       </c>
-      <c r="BQ9" s="21" t="n">
+      <c r="BQ9" s="22" t="n">
         <f aca="false">SUM(P9+AC9+AP9+BC9+BP9)</f>
         <v>0</v>
       </c>
-      <c r="BR9" s="25"/>
-      <c r="BS9" s="19" t="n">
+      <c r="BR9" s="26"/>
+      <c r="BS9" s="20" t="n">
         <f aca="false">SUM(C9+BR9)</f>
         <v>0</v>
       </c>
-      <c r="BT9" s="25" t="n">
+      <c r="BT9" s="26" t="n">
         <f aca="false">IF((C9+BR9)/2&lt;=1.5,1,IF(BR9=1,1,ROUND((C9+BR9)/2,0)))</f>
         <v>1</v>
       </c>
-      <c r="BU9" s="19"/>
-      <c r="BV9" s="19"/>
+      <c r="BU9" s="20"/>
+      <c r="BV9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="20" t="n">
         <f aca="false">PLANTILLA_ETAPA_1!BQ10</f>
         <v>0</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="24" t="n">
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="25" t="n">
         <f aca="false">SUM(D10:O10)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="24" t="n">
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="25" t="n">
         <f aca="false">SUM(Q10:AB10)</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="19"/>
-      <c r="AG10" s="19"/>
-      <c r="AH10" s="19"/>
-      <c r="AI10" s="19"/>
-      <c r="AJ10" s="19"/>
-      <c r="AK10" s="19"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="19"/>
-      <c r="AN10" s="19"/>
-      <c r="AO10" s="19"/>
-      <c r="AP10" s="24" t="n">
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="20"/>
+      <c r="AK10" s="20"/>
+      <c r="AL10" s="20"/>
+      <c r="AM10" s="20"/>
+      <c r="AN10" s="20"/>
+      <c r="AO10" s="20"/>
+      <c r="AP10" s="25" t="n">
         <f aca="false">SUM(AD10:AO10)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="19"/>
-      <c r="AR10" s="19"/>
-      <c r="AS10" s="19"/>
-      <c r="AT10" s="19"/>
-      <c r="AU10" s="19"/>
-      <c r="AV10" s="19"/>
-      <c r="AW10" s="19"/>
-      <c r="AX10" s="19"/>
-      <c r="AY10" s="19"/>
-      <c r="AZ10" s="19"/>
-      <c r="BA10" s="19"/>
-      <c r="BB10" s="19"/>
-      <c r="BC10" s="24" t="n">
+      <c r="AQ10" s="20"/>
+      <c r="AR10" s="20"/>
+      <c r="AS10" s="20"/>
+      <c r="AT10" s="20"/>
+      <c r="AU10" s="20"/>
+      <c r="AV10" s="20"/>
+      <c r="AW10" s="20"/>
+      <c r="AX10" s="20"/>
+      <c r="AY10" s="20"/>
+      <c r="AZ10" s="20"/>
+      <c r="BA10" s="20"/>
+      <c r="BB10" s="20"/>
+      <c r="BC10" s="25" t="n">
         <f aca="false">SUM(AQ10:BB10)</f>
         <v>0</v>
       </c>
-      <c r="BD10" s="19"/>
-      <c r="BE10" s="19"/>
-      <c r="BF10" s="19"/>
-      <c r="BG10" s="19"/>
-      <c r="BH10" s="19"/>
-      <c r="BI10" s="19"/>
-      <c r="BJ10" s="19"/>
-      <c r="BK10" s="19"/>
-      <c r="BL10" s="19"/>
-      <c r="BM10" s="19"/>
-      <c r="BN10" s="19"/>
-      <c r="BO10" s="19"/>
-      <c r="BP10" s="24" t="n">
+      <c r="BD10" s="20"/>
+      <c r="BE10" s="20"/>
+      <c r="BF10" s="20"/>
+      <c r="BG10" s="20"/>
+      <c r="BH10" s="20"/>
+      <c r="BI10" s="20"/>
+      <c r="BJ10" s="20"/>
+      <c r="BK10" s="20"/>
+      <c r="BL10" s="20"/>
+      <c r="BM10" s="20"/>
+      <c r="BN10" s="20"/>
+      <c r="BO10" s="20"/>
+      <c r="BP10" s="25" t="n">
         <f aca="false">SUM(BD10:BO10)</f>
         <v>0</v>
       </c>
-      <c r="BQ10" s="21" t="n">
+      <c r="BQ10" s="22" t="n">
         <f aca="false">SUM(P10+AC10+AP10+BC10+BP10)</f>
         <v>0</v>
       </c>
-      <c r="BR10" s="25"/>
-      <c r="BS10" s="19" t="n">
+      <c r="BR10" s="26"/>
+      <c r="BS10" s="20" t="n">
         <f aca="false">SUM(C10+BR10)</f>
         <v>0</v>
       </c>
-      <c r="BT10" s="25" t="n">
+      <c r="BT10" s="26" t="n">
         <f aca="false">IF((C10+BR10)/2&lt;=1.5,1,IF(BR10=1,1,ROUND((C10+BR10)/2,0)))</f>
         <v>1</v>
       </c>
-      <c r="BU10" s="19"/>
-      <c r="BV10" s="19"/>
+      <c r="BU10" s="20"/>
+      <c r="BV10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="20" t="n">
         <f aca="false">PLANTILLA_ETAPA_1!BQ11</f>
         <v>0</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="24" t="n">
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="25" t="n">
         <f aca="false">SUM(D11:O11)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="24" t="n">
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="25" t="n">
         <f aca="false">SUM(Q11:AB11)</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="19"/>
-      <c r="AP11" s="24" t="n">
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20"/>
+      <c r="AJ11" s="20"/>
+      <c r="AK11" s="20"/>
+      <c r="AL11" s="20"/>
+      <c r="AM11" s="20"/>
+      <c r="AN11" s="20"/>
+      <c r="AO11" s="20"/>
+      <c r="AP11" s="25" t="n">
         <f aca="false">SUM(AD11:AO11)</f>
         <v>0</v>
       </c>
-      <c r="AQ11" s="19"/>
-      <c r="AR11" s="19"/>
-      <c r="AS11" s="19"/>
-      <c r="AT11" s="19"/>
-      <c r="AU11" s="19"/>
-      <c r="AV11" s="19"/>
-      <c r="AW11" s="19"/>
-      <c r="AX11" s="19"/>
-      <c r="AY11" s="19"/>
-      <c r="AZ11" s="19"/>
-      <c r="BA11" s="19"/>
-      <c r="BB11" s="19"/>
-      <c r="BC11" s="24" t="n">
+      <c r="AQ11" s="20"/>
+      <c r="AR11" s="20"/>
+      <c r="AS11" s="20"/>
+      <c r="AT11" s="20"/>
+      <c r="AU11" s="20"/>
+      <c r="AV11" s="20"/>
+      <c r="AW11" s="20"/>
+      <c r="AX11" s="20"/>
+      <c r="AY11" s="20"/>
+      <c r="AZ11" s="20"/>
+      <c r="BA11" s="20"/>
+      <c r="BB11" s="20"/>
+      <c r="BC11" s="25" t="n">
         <f aca="false">SUM(AQ11:BB11)</f>
         <v>0</v>
       </c>
-      <c r="BD11" s="19"/>
-      <c r="BE11" s="19"/>
-      <c r="BF11" s="19"/>
-      <c r="BG11" s="19"/>
-      <c r="BH11" s="19"/>
-      <c r="BI11" s="19"/>
-      <c r="BJ11" s="19"/>
-      <c r="BK11" s="19"/>
-      <c r="BL11" s="19"/>
-      <c r="BM11" s="19"/>
-      <c r="BN11" s="19"/>
-      <c r="BO11" s="19"/>
-      <c r="BP11" s="24" t="n">
+      <c r="BD11" s="20"/>
+      <c r="BE11" s="20"/>
+      <c r="BF11" s="20"/>
+      <c r="BG11" s="20"/>
+      <c r="BH11" s="20"/>
+      <c r="BI11" s="20"/>
+      <c r="BJ11" s="20"/>
+      <c r="BK11" s="20"/>
+      <c r="BL11" s="20"/>
+      <c r="BM11" s="20"/>
+      <c r="BN11" s="20"/>
+      <c r="BO11" s="20"/>
+      <c r="BP11" s="25" t="n">
         <f aca="false">SUM(BD11:BO11)</f>
         <v>0</v>
       </c>
-      <c r="BQ11" s="21" t="n">
+      <c r="BQ11" s="22" t="n">
         <f aca="false">SUM(P11+AC11+AP11+BC11+BP11)</f>
         <v>0</v>
       </c>
-      <c r="BR11" s="25"/>
-      <c r="BS11" s="19" t="n">
+      <c r="BR11" s="26"/>
+      <c r="BS11" s="20" t="n">
         <f aca="false">SUM(C11+BR11)</f>
         <v>0</v>
       </c>
-      <c r="BT11" s="25" t="n">
+      <c r="BT11" s="26" t="n">
         <f aca="false">IF((C11+BR11)/2&lt;=1.5,1,IF(BR11=1,1,ROUND((C11+BR11)/2,0)))</f>
         <v>1</v>
       </c>
-      <c r="BU11" s="19"/>
-      <c r="BV11" s="19"/>
+      <c r="BU11" s="20"/>
+      <c r="BV11" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="11"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="11"/>
-      <c r="AJ15" s="11"/>
-      <c r="AK15" s="11"/>
-      <c r="AL15" s="11"/>
-      <c r="AM15" s="11"/>
-      <c r="AN15" s="11"/>
-      <c r="AO15" s="11"/>
-      <c r="AP15" s="11"/>
-      <c r="AQ15" s="11"/>
-      <c r="AR15" s="11"/>
-      <c r="AS15" s="11"/>
-      <c r="AT15" s="11"/>
-      <c r="AU15" s="11"/>
-      <c r="AV15" s="11"/>
-      <c r="AW15" s="11"/>
-      <c r="AX15" s="11"/>
-      <c r="AY15" s="11"/>
-      <c r="AZ15" s="11"/>
-      <c r="BA15" s="11"/>
-      <c r="BB15" s="11"/>
-      <c r="BC15" s="11"/>
-      <c r="BD15" s="11"/>
-      <c r="BE15" s="11"/>
-      <c r="BF15" s="11"/>
-      <c r="BG15" s="11"/>
-      <c r="BH15" s="11"/>
-      <c r="BI15" s="10" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="12"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="12"/>
+      <c r="AE15" s="12"/>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+      <c r="BI15" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="BJ15" s="10"/>
-      <c r="BK15" s="10"/>
-      <c r="BL15" s="10"/>
-      <c r="BM15" s="10"/>
-      <c r="BN15" s="10"/>
-      <c r="BO15" s="10"/>
-      <c r="BP15" s="10"/>
-      <c r="BQ15" s="10"/>
+      <c r="BJ15" s="11"/>
+      <c r="BK15" s="11"/>
+      <c r="BL15" s="11"/>
+      <c r="BM15" s="11"/>
+      <c r="BN15" s="11"/>
+      <c r="BO15" s="11"/>
+      <c r="BP15" s="11"/>
+      <c r="BQ15" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="28">
